--- a/test-data/test_workbook.xlsx
+++ b/test-data/test_workbook.xlsx
@@ -5,6 +5,9 @@
   <sheets>
     <sheet name="Sales" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -361,7 +364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.329999923706055" customWidth="1" min="1" max="1"/>
@@ -1029,6 +1032,211 @@
         <v/>
       </c>
       <c r="I16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ORD016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G17">
+        <f>F17*0.15</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>F17-G17</f>
+        <v/>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ORD017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>120</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G18">
+        <f>F18*0.05</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>F18-G18</f>
+        <v/>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ORD018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Keyboard</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G19">
+        <f>F19*0.05</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>F19-G19</f>
+        <v/>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ORD019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G20">
+        <f>F20*0.1</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>F20-G20</f>
+        <v/>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ORD020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G21">
+        <f>F21*0.15</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>F21-G21</f>
+        <v/>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1127,4 +1335,409 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reorder Level</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Stock Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <f>IF(C2&gt;=D2,"OK","Low")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <f>IF(C3&gt;=D3,"OK","Low")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Keyboard</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4">
+        <f>IF(C4&gt;=D4,"OK","Low")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <f>IF(C5&gt;=D5,"OK","Low")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Total Sales</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Total Units</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Avg Order Value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Order Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>SUMIF(Sales!C:C,"East",Sales!F:F)</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>SUMIF(Sales!C:C,"East",Sales!E:E)</f>
+        <v/>
+      </c>
+      <c r="D2">
+        <f>B2/E2</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>COUNTIF(Sales!C:C,"East")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>SUMIF(Sales!C:C,"West",Sales!F:F)</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>SUMIF(Sales!C:C,"West",Sales!E:E)</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>B3/E3</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>COUNTIF(Sales!C:C,"West")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>SUMIF(Sales!C:C,"South",Sales!F:F)</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>SUMIF(Sales!C:C,"South",Sales!E:E)</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>B4/E4</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>COUNTIF(Sales!C:C,"South")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>SUMIF(Sales!C:C,"North",Sales!F:F)</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>SUMIF(Sales!C:C,"North",Sales!E:E)</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>B5/E5</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>COUNTIF(Sales!C:C,"North")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>SUM(B2:B5)</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>SUM(C2:C5)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>B7/SUM(E2:E5)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUM(E2:E5)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>KPI Dashboard</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>Summary!B7</f>
+        <v/>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Units Sold</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>Summary!C7</f>
+        <v/>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>AVERAGE(Sales!F:F)</f>
+        <v/>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Highest Region</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>INDEX(Summary!A:A,MATCH(MAX(Summary!B:B),Summary!B:B,0))</f>
+        <v/>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Completed Orders</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>COUNTIF(Sales!I:I,"Completed")</f>
+        <v/>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pending Orders</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>COUNTIF(Sales!I:I,"Pending")</f>
+        <v/>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cancelled Orders</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>COUNTIF(Sales!I:I,"Cancelled")</f>
+        <v/>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>